--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D73213-30D2-4C4C-90A2-44AA8BCC2249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C4A987-9359-498B-9DF8-1581BC2DB370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="58">
   <si>
     <t xml:space="preserve">Any articles, templates, or information provided by Smartsheet on the website are for reference only. While we strive to keep the information up to date and correct, we make no representations or warranties of any kind, express or implied, about the completeness, accuracy, reliability, suitability, or availability with respect to the website or the information, articles, templates, or related graphics contained on the website. Any reliance you place on such information is therefore strictly at your own risk. </t>
   </si>
@@ -223,6 +223,12 @@
   </si>
   <si>
     <t xml:space="preserve">infer for SKIP method using CACHED infer research from NO_SKIP method </t>
+  </si>
+  <si>
+    <t>2026.03.23</t>
+  </si>
+  <si>
+    <t>iss10</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1269,7 @@
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
     </row>
-    <row r="2" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A2" s="36"/>
       <c r="B2" s="45" t="s">
         <v>8</v>
@@ -1294,7 +1300,7 @@
       <c r="N2" s="36"/>
       <c r="O2" s="36"/>
     </row>
-    <row r="3" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3" s="36"/>
       <c r="B3" s="40" t="s">
         <v>29</v>
@@ -1325,7 +1331,7 @@
       <c r="N3" s="36"/>
       <c r="O3" s="36"/>
     </row>
-    <row r="4" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="36"/>
       <c r="B4" s="40" t="s">
         <v>33</v>
@@ -1356,7 +1362,7 @@
       <c r="N4" s="36"/>
       <c r="O4" s="36"/>
     </row>
-    <row r="5" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A5" s="36"/>
       <c r="B5" s="40" t="s">
         <v>33</v>
@@ -1387,7 +1393,7 @@
       <c r="N5" s="36"/>
       <c r="O5" s="36"/>
     </row>
-    <row r="6" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A6" s="36"/>
       <c r="B6" s="40" t="s">
         <v>39</v>
@@ -1449,16 +1455,16 @@
       <c r="N7" s="36"/>
       <c r="O7" s="36"/>
     </row>
-    <row r="8" spans="1:15" s="37" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A8" s="36"/>
       <c r="B8" s="40" t="s">
         <v>45</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" s="48" t="s">
         <v>20</v>
@@ -1467,9 +1473,11 @@
         <v>27</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="41"/>
+        <v>50</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>37</v>
+      </c>
       <c r="I8" s="36"/>
       <c r="J8" s="36"/>
       <c r="K8" s="36"/>
@@ -1478,25 +1486,25 @@
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
     </row>
-    <row r="9" spans="1:15" s="37" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A9" s="36"/>
       <c r="B9" s="40" t="s">
         <v>48</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" s="48" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H9" s="41" t="s">
         <v>37</v>
@@ -1509,25 +1517,25 @@
       <c r="N9" s="36"/>
       <c r="O9" s="36"/>
     </row>
-    <row r="10" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A10" s="36"/>
       <c r="B10" s="40" t="s">
         <v>48</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D10" s="48" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F10" s="48" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H10" s="41" t="s">
         <v>37</v>
@@ -1540,13 +1548,13 @@
       <c r="N10" s="36"/>
       <c r="O10" s="36"/>
     </row>
-    <row r="11" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A11" s="36"/>
       <c r="B11" s="40" t="s">
         <v>53</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D11" s="48" t="s">
         <v>17</v>
@@ -1555,10 +1563,10 @@
         <v>20</v>
       </c>
       <c r="F11" s="48" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H11" s="41"/>
       <c r="I11" s="36"/>
@@ -1569,10 +1577,14 @@
       <c r="N11" s="36"/>
       <c r="O11" s="36"/>
     </row>
-    <row r="12" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A12" s="36"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
+      <c r="B12" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>57</v>
+      </c>
       <c r="D12" s="48" t="s">
         <v>17</v>
       </c>
@@ -1592,13 +1604,11 @@
       <c r="N12" s="36"/>
       <c r="O12" s="36"/>
     </row>
-    <row r="13" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A13" s="36"/>
       <c r="B13" s="40"/>
       <c r="C13" s="40"/>
-      <c r="D13" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D13" s="48"/>
       <c r="E13" s="48" t="s">
         <v>20</v>
       </c>
@@ -1615,13 +1625,11 @@
       <c r="N13" s="36"/>
       <c r="O13" s="36"/>
     </row>
-    <row r="14" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A14" s="36"/>
       <c r="B14" s="40"/>
       <c r="C14" s="40"/>
-      <c r="D14" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D14" s="48"/>
       <c r="E14" s="48" t="s">
         <v>20</v>
       </c>
@@ -1638,13 +1646,11 @@
       <c r="N14" s="36"/>
       <c r="O14" s="36"/>
     </row>
-    <row r="15" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A15" s="36"/>
       <c r="B15" s="40"/>
       <c r="C15" s="40"/>
-      <c r="D15" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D15" s="48"/>
       <c r="E15" s="48" t="s">
         <v>20</v>
       </c>
@@ -1661,13 +1667,11 @@
       <c r="N15" s="36"/>
       <c r="O15" s="36"/>
     </row>
-    <row r="16" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A16" s="36"/>
       <c r="B16" s="40"/>
       <c r="C16" s="40"/>
-      <c r="D16" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D16" s="48"/>
       <c r="E16" s="48" t="s">
         <v>20</v>
       </c>
@@ -1684,13 +1688,11 @@
       <c r="N16" s="36"/>
       <c r="O16" s="36"/>
     </row>
-    <row r="17" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A17" s="36"/>
       <c r="B17" s="40"/>
       <c r="C17" s="40"/>
-      <c r="D17" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D17" s="48"/>
       <c r="E17" s="48" t="s">
         <v>20</v>
       </c>
@@ -1707,13 +1709,11 @@
       <c r="N17" s="36"/>
       <c r="O17" s="36"/>
     </row>
-    <row r="18" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A18" s="36"/>
       <c r="B18" s="40"/>
       <c r="C18" s="40"/>
-      <c r="D18" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D18" s="48"/>
       <c r="E18" s="48" t="s">
         <v>20</v>
       </c>
@@ -1730,13 +1730,11 @@
       <c r="N18" s="36"/>
       <c r="O18" s="36"/>
     </row>
-    <row r="19" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A19" s="36"/>
       <c r="B19" s="40"/>
       <c r="C19" s="40"/>
-      <c r="D19" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D19" s="48"/>
       <c r="E19" s="48" t="s">
         <v>20</v>
       </c>
@@ -1753,13 +1751,11 @@
       <c r="N19" s="36"/>
       <c r="O19" s="36"/>
     </row>
-    <row r="20" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A20" s="36"/>
       <c r="B20" s="40"/>
       <c r="C20" s="40"/>
-      <c r="D20" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D20" s="48"/>
       <c r="E20" s="48" t="s">
         <v>20</v>
       </c>
@@ -1776,13 +1772,11 @@
       <c r="N20" s="36"/>
       <c r="O20" s="36"/>
     </row>
-    <row r="21" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A21" s="36"/>
       <c r="B21" s="40"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D21" s="48"/>
       <c r="E21" s="48" t="s">
         <v>20</v>
       </c>
@@ -1799,13 +1793,11 @@
       <c r="N21" s="36"/>
       <c r="O21" s="36"/>
     </row>
-    <row r="22" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A22" s="36"/>
       <c r="B22" s="40"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D22" s="48"/>
       <c r="E22" s="48" t="s">
         <v>20</v>
       </c>
@@ -1822,13 +1814,11 @@
       <c r="N22" s="36"/>
       <c r="O22" s="36"/>
     </row>
-    <row r="23" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A23" s="36"/>
       <c r="B23" s="40"/>
       <c r="C23" s="40"/>
-      <c r="D23" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D23" s="48"/>
       <c r="E23" s="48" t="s">
         <v>20</v>
       </c>
@@ -1845,13 +1835,11 @@
       <c r="N23" s="36"/>
       <c r="O23" s="36"/>
     </row>
-    <row r="24" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A24" s="36"/>
       <c r="B24" s="40"/>
       <c r="C24" s="40"/>
-      <c r="D24" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D24" s="48"/>
       <c r="E24" s="48" t="s">
         <v>20</v>
       </c>
@@ -1868,13 +1856,11 @@
       <c r="N24" s="36"/>
       <c r="O24" s="36"/>
     </row>
-    <row r="25" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A25" s="36"/>
       <c r="B25" s="40"/>
       <c r="C25" s="40"/>
-      <c r="D25" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D25" s="48"/>
       <c r="E25" s="48" t="s">
         <v>20</v>
       </c>
@@ -1891,13 +1877,11 @@
       <c r="N25" s="36"/>
       <c r="O25" s="36"/>
     </row>
-    <row r="26" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A26" s="36"/>
       <c r="B26" s="40"/>
       <c r="C26" s="40"/>
-      <c r="D26" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D26" s="48"/>
       <c r="E26" s="48" t="s">
         <v>20</v>
       </c>
@@ -1914,13 +1898,11 @@
       <c r="N26" s="36"/>
       <c r="O26" s="36"/>
     </row>
-    <row r="27" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A27" s="36"/>
       <c r="B27" s="40"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D27" s="48"/>
       <c r="E27" s="48" t="s">
         <v>20</v>
       </c>

--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C4A987-9359-498B-9DF8-1581BC2DB370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A724975C-C837-4CCC-845C-AACF83BF75FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Blank Issue Tracking'!$B$7:$L$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Example Issue Tracking'!$C$2:$H$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Blank Issue Tracking'!$B$2:$L$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Example Issue Tracking'!$C$1:$H$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Example Issue Tracking'!$C$1:$H$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="59">
   <si>
     <t xml:space="preserve">Any articles, templates, or information provided by Smartsheet on the website are for reference only. While we strive to keep the information up to date and correct, we make no representations or warranties of any kind, express or implied, about the completeness, accuracy, reliability, suitability, or availability with respect to the website or the information, articles, templates, or related graphics contained on the website. Any reliance you place on such information is therefore strictly at your own risk. </t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>iss10</t>
+  </si>
+  <si>
+    <t>use pre-computed give wrong elapsed_time (do not use the elapsed_time in no_skip csv for final compute elapsed time)</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1248,7 @@
     <tabColor theme="3" tint="0.89999084444715716"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O710"/>
+  <dimension ref="A1:O709"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.625" style="32" customWidth="1"/>
@@ -1557,7 +1560,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E11" s="48" t="s">
         <v>20</v>
@@ -1568,7 +1571,9 @@
       <c r="G11" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="41"/>
+      <c r="H11" s="41" t="s">
+        <v>37</v>
+      </c>
       <c r="I11" s="36"/>
       <c r="J11" s="36"/>
       <c r="K11" s="36"/>
@@ -1577,7 +1582,7 @@
       <c r="N11" s="36"/>
       <c r="O11" s="36"/>
     </row>
-    <row r="12" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" s="37" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="36"/>
       <c r="B12" s="40" t="s">
         <v>56</v>
@@ -1594,7 +1599,9 @@
       <c r="F12" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="39"/>
+      <c r="G12" s="39" t="s">
+        <v>58</v>
+      </c>
       <c r="H12" s="41"/>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -1898,26 +1905,14 @@
       <c r="N26" s="36"/>
       <c r="O26" s="36"/>
     </row>
-    <row r="27" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="F27" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="39"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="36"/>
+    <row r="27" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
     </row>
     <row r="28" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="32"/>
@@ -4176,7 +4171,7 @@
       <c r="E278" s="32"/>
       <c r="F278" s="34"/>
       <c r="G278" s="32"/>
-      <c r="H278" s="32"/>
+      <c r="H278" s="42"/>
     </row>
     <row r="279" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B279" s="32"/>
@@ -5718,13 +5713,7 @@
       <c r="H449" s="42"/>
     </row>
     <row r="450" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B450" s="32"/>
-      <c r="C450" s="32"/>
-      <c r="D450" s="34"/>
-      <c r="E450" s="32"/>
-      <c r="F450" s="34"/>
-      <c r="G450" s="32"/>
-      <c r="H450" s="42"/>
+      <c r="H450" s="44"/>
     </row>
     <row r="451" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H451" s="44"/>
@@ -6502,9 +6491,6 @@
     </row>
     <row r="709" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H709" s="44"/>
-    </row>
-    <row r="710" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H710" s="44"/>
     </row>
   </sheetData>
   <autoFilter ref="C2:H2" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -6513,7 +6499,7 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="17" type="noConversion"/>
-  <conditionalFormatting sqref="D3:F27">
+  <conditionalFormatting sqref="D3:F26">
     <cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="Closed">
       <formula>NOT(ISERROR(SEARCH("Closed",D3)))</formula>
     </cfRule>
@@ -6524,7 +6510,7 @@
       <formula>NOT(ISERROR(SEARCH("Open",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E27">
+  <conditionalFormatting sqref="E3:E26">
     <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="Request">
       <formula>NOT(ISERROR(SEARCH("Request",E3)))</formula>
     </cfRule>
@@ -6538,7 +6524,7 @@
       <formula>NOT(ISERROR(SEARCH("Bug",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F27">
+  <conditionalFormatting sqref="F3:F26">
     <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",F3)))</formula>
     </cfRule>
@@ -6561,19 +6547,19 @@
           <x14:formula1>
             <xm:f>'Key - Do Not Delete'!$D$4:$D$7</xm:f>
           </x14:formula1>
-          <xm:sqref>F3:F27</xm:sqref>
+          <xm:sqref>F3:F26</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1F940809-3D47-438D-8CB1-D74B7C055D52}">
           <x14:formula1>
             <xm:f>'Key - Do Not Delete'!$C$4:$C$7</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E27</xm:sqref>
+          <xm:sqref>E3:E26</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F499DE9E-388C-4FE3-96A1-CE14ABE25F5D}">
           <x14:formula1>
             <xm:f>'Key - Do Not Delete'!$B$4:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:F27</xm:sqref>
+          <xm:sqref>D3:F26</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A724975C-C837-4CCC-845C-AACF83BF75FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24615EA-AA9D-4B04-B581-54A5AB9C5ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24615EA-AA9D-4B04-B581-54A5AB9C5ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C833ABB-2376-4490-AA56-7299F78F37BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="285" windowWidth="28110" windowHeight="16035" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Issue Tracking" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="62">
   <si>
     <t xml:space="preserve">Any articles, templates, or information provided by Smartsheet on the website are for reference only. While we strive to keep the information up to date and correct, we make no representations or warranties of any kind, express or implied, about the completeness, accuracy, reliability, suitability, or availability with respect to the website or the information, articles, templates, or related graphics contained on the website. Any reliance you place on such information is therefore strictly at your own risk. </t>
   </si>
@@ -232,6 +232,30 @@
   </si>
   <si>
     <t>use pre-computed give wrong elapsed_time (do not use the elapsed_time in no_skip csv for final compute elapsed time)</t>
+  </si>
+  <si>
+    <t>iss11</t>
+  </si>
+  <si>
+    <t>2026.03.27</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t>NO_CROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t xml:space="preserve"> for skip  module + update Skip module using FrameDiff</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1591,7 +1615,7 @@
         <v>57</v>
       </c>
       <c r="D12" s="48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E12" s="48" t="s">
         <v>20</v>
@@ -1613,16 +1637,24 @@
     </row>
     <row r="13" spans="1:15" s="37" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A13" s="36"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="48"/>
+      <c r="B13" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>17</v>
+      </c>
       <c r="E13" s="48" t="s">
         <v>20</v>
       </c>
       <c r="F13" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="39"/>
+      <c r="G13" s="39" t="s">
+        <v>61</v>
+      </c>
       <c r="H13" s="41"/>
       <c r="I13" s="36"/>
       <c r="J13" s="36"/>

--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C833ABB-2376-4490-AA56-7299F78F37BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CFCAD09-D519-4373-99CB-1011FF11FD49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="285" windowWidth="28110" windowHeight="16035" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="62">
   <si>
     <t xml:space="preserve">Any articles, templates, or information provided by Smartsheet on the website are for reference only. While we strive to keep the information up to date and correct, we make no representations or warranties of any kind, express or implied, about the completeness, accuracy, reliability, suitability, or availability with respect to the website or the information, articles, templates, or related graphics contained on the website. Any reliance you place on such information is therefore strictly at your own risk. </t>
   </si>
@@ -1626,7 +1626,9 @@
       <c r="G12" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="41"/>
+      <c r="H12" s="41" t="s">
+        <v>37</v>
+      </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
       <c r="K12" s="36"/>

--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B252EE4-943E-43FA-ADCE-A5347615224C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271ACF9B-432C-48D7-B675-0E593E584478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="285" windowWidth="28110" windowHeight="16035" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="54">
   <si>
     <t>Status</t>
   </si>
@@ -6225,32 +6225,13 @@
       <formula>NOT(ISERROR(SEARCH("Low",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:F26" xr:uid="{0FE1C215-D2BB-457C-B71B-3AD1725D56C1}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0" footer="0"/>
   <pageSetup scale="60" fitToHeight="0" orientation="landscape" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0FE1C215-D2BB-457C-B71B-3AD1725D56C1}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>F3:F26</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1F940809-3D47-438D-8CB1-D74B7C055D52}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>E3:E26</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F499DE9E-388C-4FE3-96A1-CE14ABE25F5D}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>D3:F26</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -6318,103 +6299,210 @@
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
+      <c r="B4" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="20">
+        <v>96</v>
+      </c>
+      <c r="E4" s="20">
+        <v>275</v>
+      </c>
+      <c r="F4" s="20" t="str">
+        <f>TEXT(E4/86400,"[h]:mm:ss")</f>
+        <v>0:04:35</v>
+      </c>
+      <c r="G4" s="20">
+        <f>D4*E4</f>
+        <v>26400</v>
+      </c>
+      <c r="H4" s="20" t="str">
+        <f t="shared" ref="H4:H14" si="0">TEXT(G4/86400,"[h]:mm:ss")</f>
+        <v>7:20:00</v>
+      </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
       <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
+      <c r="F5" s="20" t="str">
+        <f t="shared" ref="F5:F14" si="1">TEXT(E5/86400,"[h]:mm:ss")</f>
+        <v>0:00:00</v>
+      </c>
+      <c r="G5" s="20">
+        <f t="shared" ref="G5:G14" si="2">D5*E5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
       <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
+      <c r="F6" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G6" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
+      <c r="F7" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G7" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
+      <c r="F8" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G8" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
+      <c r="F9" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G9" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
+      <c r="F10" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G10" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
+      <c r="F11" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G11" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
+      <c r="F12" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G12" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
       <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
+      <c r="F13" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G13" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
+      <c r="F14" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G14" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271ACF9B-432C-48D7-B675-0E593E584478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953278DD-33FF-4F7B-99FC-9635AB5327F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="285" windowWidth="28110" windowHeight="16035" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Issue Tracking" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="57">
   <si>
     <t>Status</t>
   </si>
@@ -228,6 +228,15 @@
   </si>
   <si>
     <t>otp_frame_diff</t>
+  </si>
+  <si>
+    <t>2026.04.15</t>
+  </si>
+  <si>
+    <t>iss12</t>
+  </si>
+  <si>
+    <t>update table in (zpaper2) that show metrics having arrow and hightlight best+ second best</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1308,7 @@
         <v>42</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>8</v>
@@ -1319,18 +1328,26 @@
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
     </row>
-    <row r="14" spans="1:15" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" s="6" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="17"/>
+      <c r="B14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>6</v>
+      </c>
       <c r="E14" s="17" t="s">
         <v>8</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="8"/>
+      <c r="G14" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="H14" s="10"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
@@ -6225,9 +6242,12 @@
       <formula>NOT(ISERROR(SEARCH("Low",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:F26" xr:uid="{0FE1C215-D2BB-457C-B71B-3AD1725D56C1}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:F26 D15:D26" xr:uid="{0FE1C215-D2BB-457C-B71B-3AD1725D56C1}">
       <formula1>#REF!</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D14" xr:uid="{49DD096F-692D-432E-8379-3E1D921F826C}">
+      <formula1>"Open, Closed, On Hold"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0" footer="0"/>

--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953278DD-33FF-4F7B-99FC-9635AB5327F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441A7361-FDCC-4FE7-9192-87B5DD5977D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="56">
   <si>
     <t>Status</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>Comments</t>
-  </si>
-  <si>
-    <t>Open</t>
   </si>
   <si>
     <t>Closed</t>
@@ -964,7 +961,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>0</v>
@@ -992,25 +989,25 @@
     <row r="3" spans="1:15" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="H3" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -1023,25 +1020,25 @@
     <row r="4" spans="1:15" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="D4" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="17" t="s">
-        <v>8</v>
-      </c>
       <c r="F4" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>20</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -1054,25 +1051,25 @@
     <row r="5" spans="1:15" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>8</v>
-      </c>
       <c r="F5" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -1085,25 +1082,25 @@
     <row r="6" spans="1:15" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="H6" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -1116,25 +1113,25 @@
     <row r="7" spans="1:15" s="6" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="H7" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
@@ -1147,25 +1144,25 @@
     <row r="8" spans="1:15" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>33</v>
-      </c>
       <c r="H8" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -1178,25 +1175,25 @@
     <row r="9" spans="1:15" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="H9" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
@@ -1209,25 +1206,25 @@
     <row r="10" spans="1:15" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="H10" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -1240,25 +1237,25 @@
     <row r="11" spans="1:15" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>24</v>
-      </c>
       <c r="H11" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -1271,25 +1268,25 @@
     <row r="12" spans="1:15" s="6" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="H12" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -1302,22 +1299,22 @@
     <row r="13" spans="1:15" s="6" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>43</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>44</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="5"/>
@@ -1331,22 +1328,22 @@
     <row r="14" spans="1:15" s="6" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>55</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H14" s="10"/>
       <c r="I14" s="5"/>
@@ -1363,10 +1360,10 @@
       <c r="C15" s="9"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="10"/>
@@ -1384,10 +1381,10 @@
       <c r="C16" s="9"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="10"/>
@@ -1405,10 +1402,10 @@
       <c r="C17" s="9"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="10"/>
@@ -1426,10 +1423,10 @@
       <c r="C18" s="9"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="10"/>
@@ -1447,10 +1444,10 @@
       <c r="C19" s="9"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="10"/>
@@ -1468,10 +1465,10 @@
       <c r="C20" s="9"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="10"/>
@@ -1489,10 +1486,10 @@
       <c r="C21" s="9"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="10"/>
@@ -1510,10 +1507,10 @@
       <c r="C22" s="9"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="10"/>
@@ -1531,10 +1528,10 @@
       <c r="C23" s="9"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="10"/>
@@ -1552,10 +1549,10 @@
       <c r="C24" s="9"/>
       <c r="D24" s="17"/>
       <c r="E24" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="10"/>
@@ -1573,10 +1570,10 @@
       <c r="C25" s="9"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="10"/>
@@ -1594,10 +1591,10 @@
       <c r="C26" s="9"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="10"/>
@@ -6271,33 +6268,33 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="19" t="s">
         <v>46</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="20">
         <v>48</v>
@@ -6320,10 +6317,10 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="20">
         <v>96</v>

--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2DBC0B-5552-479E-9A51-F6BA8F944287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A994FE91-1BFE-4F71-B48C-125A95CE1CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1435,7 +1435,7 @@
         <v>60</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>7</v>

--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A994FE91-1BFE-4F71-B48C-125A95CE1CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061675FC-93FA-45A4-B65E-5C09CC8A8663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="69">
   <si>
     <t>Status</t>
   </si>
@@ -1406,7 +1406,7 @@
         <v>55</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>7</v>
@@ -1417,7 +1417,9 @@
       <c r="G15" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="17"/>
+      <c r="H15" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
@@ -1435,7 +1437,7 @@
         <v>60</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>7</v>
@@ -1493,7 +1495,7 @@
         <v>64</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>8</v>

--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061675FC-93FA-45A4-B65E-5C09CC8A8663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061D6398-94AF-4638-B560-97C8B06319C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="285" windowWidth="28110" windowHeight="16035" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Issue Tracking" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="74">
   <si>
     <t>Status</t>
   </si>
@@ -273,6 +273,21 @@
   </si>
   <si>
     <t>On Hold</t>
+  </si>
+  <si>
+    <t>2026.04.21</t>
+  </si>
+  <si>
+    <t>iss18</t>
+  </si>
+  <si>
+    <t>update FPS of all table based on pre-computed NoTemp in MainPC</t>
+  </si>
+  <si>
+    <t>opt_accMotionDet</t>
+  </si>
+  <si>
+    <t>opt_Tpt</t>
   </si>
 </sst>
 </file>
@@ -1546,14 +1561,24 @@
     </row>
     <row r="20" spans="1:15" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
+      <c r="B20" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>8</v>
+      </c>
       <c r="F20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="16"/>
+      <c r="G20" s="16" t="s">
+        <v>71</v>
+      </c>
       <c r="H20" s="17"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
@@ -6323,7 +6348,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7244F240-3E57-47A4-933B-A5E0C8789D48}">
-  <dimension ref="B2:H14"/>
+  <dimension ref="B2:H13"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.625" customWidth="1"/>
@@ -6386,7 +6411,7 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>46</v>
@@ -6394,37 +6419,41 @@
       <c r="D4" s="2">
         <v>96</v>
       </c>
-      <c r="E4" s="2">
-        <v>275</v>
-      </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="2" t="str">
-        <f>TEXT(E4/86400,"[h]:mm:ss")</f>
-        <v>0:04:35</v>
+        <f t="shared" ref="F4:F13" si="0">TEXT(E4/86400,"[h]:mm:ss")</f>
+        <v>0:00:00</v>
       </c>
       <c r="G4" s="2">
-        <f>D4*E4</f>
-        <v>26400</v>
+        <f t="shared" ref="G4:G13" si="1">D4*E4</f>
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="str">
-        <f t="shared" ref="H4:H14" si="0">TEXT(G4/86400,"[h]:mm:ss")</f>
-        <v>7:20:00</v>
+        <f t="shared" ref="H4:H13" si="2">TEXT(G4/86400,"[h]:mm:ss")</f>
+        <v>0:00:00</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="2">
+        <v>126</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="str">
-        <f t="shared" ref="F5:F14" si="1">TEXT(E5/86400,"[h]:mm:ss")</f>
+        <f t="shared" si="0"/>
         <v>0:00:00</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" ref="G5:G14" si="2">D5*E5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H5" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0:00:00</v>
       </c>
     </row>
@@ -6434,15 +6463,15 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G6" s="2">
         <f t="shared" si="1"/>
-        <v>0:00:00</v>
-      </c>
-      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="str">
-        <f t="shared" si="0"/>
         <v>0:00:00</v>
       </c>
     </row>
@@ -6452,15 +6481,15 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G7" s="2">
         <f t="shared" si="1"/>
-        <v>0:00:00</v>
-      </c>
-      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="str">
-        <f t="shared" si="0"/>
         <v>0:00:00</v>
       </c>
     </row>
@@ -6470,15 +6499,15 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G8" s="2">
         <f t="shared" si="1"/>
-        <v>0:00:00</v>
-      </c>
-      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="str">
-        <f t="shared" si="0"/>
         <v>0:00:00</v>
       </c>
     </row>
@@ -6488,15 +6517,15 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G9" s="2">
         <f t="shared" si="1"/>
-        <v>0:00:00</v>
-      </c>
-      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="str">
-        <f t="shared" si="0"/>
         <v>0:00:00</v>
       </c>
     </row>
@@ -6506,15 +6535,15 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G10" s="2">
         <f t="shared" si="1"/>
-        <v>0:00:00</v>
-      </c>
-      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="2" t="str">
-        <f t="shared" si="0"/>
         <v>0:00:00</v>
       </c>
     </row>
@@ -6524,15 +6553,15 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G11" s="2">
         <f t="shared" si="1"/>
-        <v>0:00:00</v>
-      </c>
-      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="2" t="str">
-        <f t="shared" si="0"/>
         <v>0:00:00</v>
       </c>
     </row>
@@ -6542,15 +6571,15 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>0:00:00</v>
+      </c>
+      <c r="G12" s="2">
         <f t="shared" si="1"/>
-        <v>0:00:00</v>
-      </c>
-      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="2" t="str">
-        <f t="shared" si="0"/>
         <v>0:00:00</v>
       </c>
     </row>
@@ -6560,33 +6589,15 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>0:00:00</v>
-      </c>
-      <c r="G13" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0:00:00</v>
       </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="str">
+      <c r="G13" s="2">
         <f t="shared" si="1"/>
-        <v>0:00:00</v>
-      </c>
-      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="str">
-        <f t="shared" si="0"/>
         <v>0:00:00</v>
       </c>
     </row>

--- a/_TODO.xlsx
+++ b/_TODO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061D6398-94AF-4638-B560-97C8B06319C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F43721-C253-4D39-992A-C161B453F957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="285" windowWidth="28110" windowHeight="16035" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Issue Tracking" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="87">
   <si>
     <t>Status</t>
   </si>
@@ -263,9 +263,6 @@
     <t>iss16</t>
   </si>
   <si>
-    <t>Skip  module with feedback from BIG MODEL (if big model confirm fire/smoke fore few frames, then ignore SKIP for a specific period)</t>
-  </si>
-  <si>
     <t>iss17</t>
   </si>
   <si>
@@ -288,6 +285,48 @@
   </si>
   <si>
     <t>opt_Tpt</t>
+  </si>
+  <si>
+    <t>Eager mode: implementation + update report (Hyperparam search on Val + Results on Test set)</t>
+  </si>
+  <si>
+    <t>2026.05.12</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Update the text describing the training of BIG Model</t>
+  </si>
+  <si>
+    <t>iss19</t>
+  </si>
+  <si>
+    <t>RE-check + Update all Paper2 content (to make sure it consistent)</t>
+  </si>
+  <si>
+    <t>iss20</t>
+  </si>
+  <si>
+    <t>Merge Paper2 Content into Thesis</t>
+  </si>
+  <si>
+    <t>iss21</t>
+  </si>
+  <si>
+    <t>Revise Chapter 1 (Intro) + Chap2 (Literature) + Chap5 (Conclusion + Future) in the Thesis</t>
+  </si>
+  <si>
+    <t>iss22</t>
+  </si>
+  <si>
+    <t>iss23</t>
+  </si>
+  <si>
+    <t>Prepare slides for Thesis Defense</t>
+  </si>
+  <si>
+    <t>Final review the Thesis before sending out for Committee 's Review</t>
   </si>
 </sst>
 </file>
@@ -481,7 +520,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -547,6 +586,10 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1463,7 +1506,9 @@
       <c r="G16" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="17"/>
+      <c r="H16" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -1475,22 +1520,22 @@
     <row r="17" spans="1:15" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="12" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>9</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="7"/>
@@ -1501,27 +1546,29 @@
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="1:15" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>9</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18" s="17"/>
+        <v>63</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
@@ -1536,10 +1583,10 @@
         <v>54</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>8</v>
@@ -1548,7 +1595,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="7"/>
@@ -1562,10 +1609,10 @@
     <row r="20" spans="1:15" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>56</v>
@@ -1574,10 +1621,10 @@
         <v>8</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="7"/>
@@ -1590,14 +1637,24 @@
     </row>
     <row r="21" spans="1:15" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="B21" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>8</v>
+      </c>
       <c r="F21" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" s="16"/>
+        <v>75</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="H21" s="17"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
@@ -1609,14 +1666,24 @@
     </row>
     <row r="22" spans="1:15" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="B22" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>8</v>
+      </c>
       <c r="F22" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="16"/>
+        <v>75</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>78</v>
+      </c>
       <c r="H22" s="17"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
@@ -1628,14 +1695,24 @@
     </row>
     <row r="23" spans="1:15" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="B23" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>8</v>
+      </c>
       <c r="F23" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="16"/>
+        <v>75</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>80</v>
+      </c>
       <c r="H23" s="17"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
@@ -1647,14 +1724,24 @@
     </row>
     <row r="24" spans="1:15" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="B24" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>8</v>
+      </c>
       <c r="F24" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" s="16"/>
+        <v>10</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>82</v>
+      </c>
       <c r="H24" s="17"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
@@ -1666,14 +1753,24 @@
     </row>
     <row r="25" spans="1:15" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
+      <c r="B25" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>8</v>
+      </c>
       <c r="F25" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="16"/>
+        <v>10</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>86</v>
+      </c>
       <c r="H25" s="17"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
@@ -1685,14 +1782,24 @@
     </row>
     <row r="26" spans="1:15" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
+      <c r="B26" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>8</v>
+      </c>
       <c r="F26" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="16"/>
+      <c r="G26" s="16" t="s">
+        <v>85</v>
+      </c>
       <c r="H26" s="17"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
@@ -6290,6 +6397,10 @@
       <c r="H709" s="20"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:H20">
+    <sortCondition ref="D3:D20"/>
+    <sortCondition ref="B3:B20"/>
+  </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="D3:F26">
     <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="Closed">
@@ -6332,7 +6443,7 @@
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F26" xr:uid="{0FE1C215-D2BB-457C-B71B-3AD1725D56C1}">
-      <formula1>#REF!</formula1>
+      <formula1>"Critical, High, Medium, Low"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D26" xr:uid="{49DD096F-692D-432E-8379-3E1D921F826C}">
       <formula1>"Open, Closed, On Hold"</formula1>
@@ -6411,7 +6522,7 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>46</v>
@@ -6435,7 +6546,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>46</v>
